--- a/data/trans_orig/P1404-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2007</t>
+          <t>Población con diagnóstico de colesterol alto en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>23119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35945</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53944</t>
+          <t>53335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250519</t>
+          <t>249891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264239</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224893</t>
+          <t>223721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243465</t>
+          <t>243555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479904</t>
+          <t>480513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504886</t>
+          <t>504530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51761</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39577</t>
+          <t>38869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65495</t>
+          <t>65465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73428</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108522</t>
+          <t>107564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441314</t>
+          <t>441015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>465971</t>
+          <t>465255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>438454</t>
+          <t>438484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>464372</t>
+          <t>465080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>888502</t>
+          <t>889460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>923596</t>
+          <t>924570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41321</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68744</t>
+          <t>68804</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281857</t>
+          <t>282528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>301534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295910</t>
+          <t>296384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316237</t>
+          <t>316195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585514</t>
+          <t>585454</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>612937</t>
+          <t>613665</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>31450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>58677</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>323723</t>
+          <t>324741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343261</t>
+          <t>343128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339460</t>
+          <t>340006</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357132</t>
+          <t>356874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>669099</t>
+          <t>671450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696252</t>
+          <t>696316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>14483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32559</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58282</t>
+          <t>58197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167402</t>
+          <t>169696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187538</t>
+          <t>188825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>175295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194297</t>
+          <t>193680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>352694</t>
+          <t>352779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378417</t>
+          <t>377852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24364</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>27296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>41151</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67326</t>
+          <t>68361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246447</t>
+          <t>247011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261504</t>
+          <t>261689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228977</t>
+          <t>229538</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250657</t>
+          <t>250848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481629</t>
+          <t>480594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507329</t>
+          <t>507804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>55363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>89132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90748</t>
+          <t>89280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131374</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560934</t>
+          <t>562307</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>586305</t>
+          <t>585807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>551460</t>
+          <t>549087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582996</t>
+          <t>582856</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1121872</t>
+          <t>1123046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1162498</t>
+          <t>1163966</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64204</t>
+          <t>64512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98145</t>
+          <t>97595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75186</t>
+          <t>75687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111768</t>
+          <t>112994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148500</t>
+          <t>148871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197501</t>
+          <t>196638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>645650</t>
+          <t>646200</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>679591</t>
+          <t>679283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>671743</t>
+          <t>670517</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>708325</t>
+          <t>707824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1329805</t>
+          <t>1330668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1378806</t>
+          <t>1378435</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>231228</t>
+          <t>229997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>294029</t>
+          <t>291763</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>314712</t>
+          <t>312640</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>383461</t>
+          <t>385338</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>561745</t>
+          <t>561635</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>655564</t>
+          <t>658087</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2982514</t>
+          <t>2984780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3045315</t>
+          <t>3046546</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2995736</t>
+          <t>2993859</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3064485</t>
+          <t>3066557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6000177</t>
+          <t>5997654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6093996</t>
+          <t>6094106</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2012</t>
+          <t>Población con diagnóstico de colesterol alto en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41693</t>
+          <t>41802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>48598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50025</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81207</t>
+          <t>82088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253045</t>
+          <t>252936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275572</t>
+          <t>275610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>237737</t>
+          <t>238647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261457</t>
+          <t>261983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500776</t>
+          <t>499895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531958</t>
+          <t>532546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>52144</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86535</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66867</t>
+          <t>66249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99449</t>
+          <t>99614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126743</t>
+          <t>125518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173519</t>
+          <t>174092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417584</t>
+          <t>418549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452680</t>
+          <t>451975</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424316</t>
+          <t>424151</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456898</t>
+          <t>457516</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>854365</t>
+          <t>853792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901141</t>
+          <t>902366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47457</t>
+          <t>47586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58643</t>
+          <t>58877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63841</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96055</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276589</t>
+          <t>276460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300250</t>
+          <t>299140</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282377</t>
+          <t>282143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308549</t>
+          <t>308599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569011</t>
+          <t>567465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>601225</t>
+          <t>600060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58977</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49042</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77993</t>
+          <t>76648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>89252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127824</t>
+          <t>126558</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315005</t>
+          <t>314578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>341552</t>
+          <t>342918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>310958</t>
+          <t>312303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339909</t>
+          <t>339210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635109</t>
+          <t>636375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>675625</t>
+          <t>673681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24685</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61025</t>
+          <t>62556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>68967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99993</t>
+          <t>102582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165468</t>
+          <t>165706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187933</t>
+          <t>187641</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158566</t>
+          <t>157035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183481</t>
+          <t>183369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332216</t>
+          <t>329627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364227</t>
+          <t>363242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28629</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>50606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31783</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55921</t>
+          <t>55686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64440</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98148</t>
+          <t>99569</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223357</t>
+          <t>223375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>245352</t>
+          <t>247075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222175</t>
+          <t>222410</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246313</t>
+          <t>246195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>453929</t>
+          <t>452508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>487637</t>
+          <t>486034</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57276</t>
+          <t>57478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93617</t>
+          <t>92542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62572</t>
+          <t>63067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>99709</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128855</t>
+          <t>131404</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177856</t>
+          <t>180687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>569171</t>
+          <t>570246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605512</t>
+          <t>605310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594144</t>
+          <t>592184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631281</t>
+          <t>630786</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1178785</t>
+          <t>1175954</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1227786</t>
+          <t>1225237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50363</t>
+          <t>51440</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84374</t>
+          <t>86997</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78370</t>
+          <t>77415</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115178</t>
+          <t>115918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136445</t>
+          <t>136593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185303</t>
+          <t>187225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694724</t>
+          <t>692101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728735</t>
+          <t>727658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>707400</t>
+          <t>706660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>744208</t>
+          <t>745163</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1416373</t>
+          <t>1414451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1465231</t>
+          <t>1465083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>350005</t>
+          <t>349516</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>433817</t>
+          <t>429276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>451920</t>
+          <t>448403</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>534745</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>825046</t>
+          <t>822841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>935506</t>
+          <t>934543</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2991553</t>
+          <t>2996094</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3075365</t>
+          <t>3075854</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3020353</t>
+          <t>3021670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3103178</t>
+          <t>3106695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6044963</t>
+          <t>6045926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6155423</t>
+          <t>6157628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2016</t>
+          <t>Población con diagnóstico de colesterol alto en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>51899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>60619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94813</t>
+          <t>95300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243402</t>
+          <t>243661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267493</t>
+          <t>267497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234629</t>
+          <t>236804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259953</t>
+          <t>261068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487651</t>
+          <t>487164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>521828</t>
+          <t>521845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44054</t>
+          <t>43763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73330</t>
+          <t>73361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59356</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91474</t>
+          <t>93536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109428</t>
+          <t>110449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154675</t>
+          <t>155286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429245</t>
+          <t>429214</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458521</t>
+          <t>458812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>431610</t>
+          <t>429548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463728</t>
+          <t>463767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870984</t>
+          <t>870373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>916231</t>
+          <t>915210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52954</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36690</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64728</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73367</t>
+          <t>72566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111647</t>
+          <t>107871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>265611</t>
+          <t>264632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288611</t>
+          <t>287617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271581</t>
+          <t>271831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299619</t>
+          <t>298143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543227</t>
+          <t>547003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>581507</t>
+          <t>582308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>35088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61064</t>
+          <t>60878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72728</t>
+          <t>72655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85084</t>
+          <t>83619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122423</t>
+          <t>123022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308900</t>
+          <t>309086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334290</t>
+          <t>334876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314555</t>
+          <t>314628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344467</t>
+          <t>343523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634824</t>
+          <t>634225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672163</t>
+          <t>673628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43486</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,47 +8801,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>59629</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>46796</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>76677</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,89%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>59629</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>45514</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>74685</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173078</t>
+          <t>173598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191805</t>
+          <t>192899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175101</t>
+          <t>175047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194786</t>
+          <t>195222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,47 +8914,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>370179</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>353131</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>383012</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>86,13%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>82,16%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>89,11%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>370179</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>355123</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>384294</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>86,13%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>82,62%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37894</t>
+          <t>38178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42212</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72016</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225229</t>
+          <t>224945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244998</t>
+          <t>244244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>230903</t>
+          <t>232288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>253020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464222</t>
+          <t>463883</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492996</t>
+          <t>494059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55412</t>
+          <t>56626</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>90819</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56278</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89825</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122747</t>
+          <t>121723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169920</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>566893</t>
+          <t>565739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>601146</t>
+          <t>599932</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>601469</t>
+          <t>599983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>635016</t>
+          <t>634606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1177932</t>
+          <t>1178170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1225105</t>
+          <t>1226129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62955</t>
+          <t>63157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97796</t>
+          <t>96934</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94380</t>
+          <t>95341</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137120</t>
+          <t>137642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170349</t>
+          <t>166451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222411</t>
+          <t>223402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>680787</t>
+          <t>681649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>715628</t>
+          <t>715426</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>689047</t>
+          <t>688525</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>731787</t>
+          <t>730826</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1382339</t>
+          <t>1381348</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1434401</t>
+          <t>1438299</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>353120</t>
+          <t>353501</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>427140</t>
+          <t>427026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>428174</t>
+          <t>428803</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>512181</t>
+          <t>514035</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>803469</t>
+          <t>802335</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>919823</t>
+          <t>915480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2967210</t>
+          <t>2967324</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3041230</t>
+          <t>3040849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3032361</t>
+          <t>3030507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3116368</t>
+          <t>3115739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6019069</t>
+          <t>6023412</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6135423</t>
+          <t>6136557</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colesterol alto en 2023</t>
+          <t>Población con diagnóstico de colesterol alto en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>29827</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>35618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52998</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70205</t>
+          <t>69683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97825</t>
+          <t>97978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259352</t>
+          <t>260069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281872</t>
+          <t>281616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236637</t>
+          <t>234854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254474</t>
+          <t>254017</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503252</t>
+          <t>503099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530872</t>
+          <t>531394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45002</t>
+          <t>44167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>73140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54905</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80785</t>
+          <t>82226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108230</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146925</t>
+          <t>145857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440477</t>
+          <t>443389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471527</t>
+          <t>472362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>432384</t>
+          <t>430943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458264</t>
+          <t>456114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882773</t>
+          <t>883841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921468</t>
+          <t>922225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>36141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59254</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48173</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69577</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>89805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121377</t>
+          <t>121128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256247</t>
+          <t>257002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278577</t>
+          <t>279360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279551</t>
+          <t>279526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>300955</t>
+          <t>301165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543252</t>
+          <t>543501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573946</t>
+          <t>574824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65617</t>
+          <t>65118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>39589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81085</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86337</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137036</t>
+          <t>137329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246940</t>
+          <t>247439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274097</t>
+          <t>274433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>394633</t>
+          <t>391656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438537</t>
+          <t>436129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651238</t>
+          <t>650945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>701937</t>
+          <t>707207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>29948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45724</t>
+          <t>46172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45833</t>
+          <t>45669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62091</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79683</t>
+          <t>78811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102270</t>
+          <t>104021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>132570</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149057</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145345</t>
+          <t>145578</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161603</t>
+          <t>161767</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283908</t>
+          <t>282157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306495</t>
+          <t>307367</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>46517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67352</t>
+          <t>67530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53978</t>
+          <t>54397</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86595</t>
+          <t>88122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>115456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202284</t>
+          <t>202106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223870</t>
+          <t>223119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202409</t>
+          <t>201990</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219555</t>
+          <t>218875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>411459</t>
+          <t>410567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439428</t>
+          <t>437901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81742</t>
+          <t>80694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116395</t>
+          <t>117185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>148493</t>
+          <t>150158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>582751</t>
+          <t>629880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244702</t>
+          <t>245749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>859947</t>
+          <t>858019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502257</t>
+          <t>501467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>536910</t>
+          <t>537958</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>263785</t>
+          <t>216656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>698043</t>
+          <t>696378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>605241</t>
+          <t>607169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1220486</t>
+          <t>1219439</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34725</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>111109</t>
+          <t>110265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86463</t>
+          <t>86571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>120815</t>
+          <t>119732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107195</t>
+          <t>106252</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220885</t>
+          <t>218080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>817611</t>
+          <t>818455</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>893995</t>
+          <t>894766</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>594032</t>
+          <t>595115</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>628384</t>
+          <t>628276</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1422682</t>
+          <t>1425487</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1536372</t>
+          <t>1537315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>363541</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>518525</t>
+          <t>515380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>570321</t>
+          <t>572572</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1395833</t>
+          <t>1282956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1017635</t>
+          <t>1019748</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1838309</t>
+          <t>1924356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2933255</t>
+          <t>2936400</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3088239</t>
+          <t>3085792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2257022</t>
+          <t>2369899</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3082534</t>
+          <t>3080283</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5266326</t>
+          <t>5180279</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6087000</t>
+          <t>6084887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1404-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1404-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>22770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>53160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249891</t>
+          <t>250240</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264113</t>
+          <t>264352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>223721</t>
+          <t>223886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243555</t>
+          <t>242897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480513</t>
+          <t>480688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504530</t>
+          <t>504709</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>49787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38869</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65465</t>
+          <t>65487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>72379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107564</t>
+          <t>107690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441015</t>
+          <t>443288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>465255</t>
+          <t>467255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>438484</t>
+          <t>438462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465080</t>
+          <t>464923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>889460</t>
+          <t>889334</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>924570</t>
+          <t>924645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39028</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40593</t>
+          <t>40167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68804</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282528</t>
+          <t>282637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301534</t>
+          <t>301435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296384</t>
+          <t>296562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316195</t>
+          <t>316596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585454</t>
+          <t>586653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613665</t>
+          <t>614091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>33765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>32233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58677</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324741</t>
+          <t>324906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>343128</t>
+          <t>343492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>340006</t>
+          <t>339223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356874</t>
+          <t>356405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>671450</t>
+          <t>669551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696316</t>
+          <t>695624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33951</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>31792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58197</t>
+          <t>58256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169696</t>
+          <t>169357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188825</t>
+          <t>188088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175295</t>
+          <t>175876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193680</t>
+          <t>194081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>352779</t>
+          <t>352720</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377852</t>
+          <t>378620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48606</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>40898</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>68015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247011</t>
+          <t>246377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261689</t>
+          <t>262039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229538</t>
+          <t>228517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250848</t>
+          <t>251215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>480594</t>
+          <t>480940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507804</t>
+          <t>508057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>28071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52586</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55363</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89132</t>
+          <t>85885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89280</t>
+          <t>90170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130200</t>
+          <t>129546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>562441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>585807</t>
+          <t>586956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>549087</t>
+          <t>552334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>582856</t>
+          <t>583681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1123046</t>
+          <t>1123700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1163966</t>
+          <t>1163076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97595</t>
+          <t>99397</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75687</t>
+          <t>73846</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>110024</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148871</t>
+          <t>148564</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196638</t>
+          <t>197567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>646200</t>
+          <t>644398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>679283</t>
+          <t>679665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>670517</t>
+          <t>673487</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>707824</t>
+          <t>709665</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1330668</t>
+          <t>1329739</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1378435</t>
+          <t>1378742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229997</t>
+          <t>227814</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>291763</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>312640</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>385338</t>
+          <t>383320</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>561635</t>
+          <t>562402</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>658087</t>
+          <t>654366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2984780</t>
+          <t>2985716</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3046546</t>
+          <t>3048729</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2993859</t>
+          <t>2995877</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3066557</t>
+          <t>3066967</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5997654</t>
+          <t>6001375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6094106</t>
+          <t>6093339</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41802</t>
+          <t>41243</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25262</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>49694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49437</t>
+          <t>51384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82088</t>
+          <t>82926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252936</t>
+          <t>253495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275610</t>
+          <t>275717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238647</t>
+          <t>237551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261983</t>
+          <t>261677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499895</t>
+          <t>499057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>532546</t>
+          <t>530599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>51979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85570</t>
+          <t>85391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66249</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99614</t>
+          <t>100656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125518</t>
+          <t>126009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174092</t>
+          <t>173422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418549</t>
+          <t>418728</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451975</t>
+          <t>452140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424151</t>
+          <t>423109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457516</t>
+          <t>457192</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853792</t>
+          <t>854462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902366</t>
+          <t>901875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>46823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>34318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58877</t>
+          <t>60365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65006</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97601</t>
+          <t>99484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276460</t>
+          <t>277223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299140</t>
+          <t>299126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>282143</t>
+          <t>280655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308599</t>
+          <t>306702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567465</t>
+          <t>565582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600060</t>
+          <t>602366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31064</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>58661</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89252</t>
+          <t>88937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126558</t>
+          <t>127918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>314578</t>
+          <t>315321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342918</t>
+          <t>342099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>312303</t>
+          <t>310269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339210</t>
+          <t>339747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>636375</t>
+          <t>635015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673681</t>
+          <t>673996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>47516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>36614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68967</t>
+          <t>65545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102582</t>
+          <t>99579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165706</t>
+          <t>165102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187641</t>
+          <t>187701</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157035</t>
+          <t>157734</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183369</t>
+          <t>182977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329627</t>
+          <t>332630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363242</t>
+          <t>366664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,83%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50606</t>
+          <t>49267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,82 +5786,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>43540</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>31588</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>55598</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>81685</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>66115</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>101961</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>18,47%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>43540</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>31901</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>55686</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>81685</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>66043</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>99569</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223375</t>
+          <t>224714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247075</t>
+          <t>246770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,82 +5899,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>82,02%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>234556</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>222498</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>246508</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>84,34%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>80,01%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>470392</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>450116</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>485962</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>85,2%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>81,53%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,18%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>234556</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>222410</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>246195</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>84,34%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>470392</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>452508</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>486034</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>85,2%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57478</t>
+          <t>59610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92542</t>
+          <t>95055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63067</t>
+          <t>63037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>101669</t>
+          <t>98266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131404</t>
+          <t>129893</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180687</t>
+          <t>181394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570246</t>
+          <t>567733</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605310</t>
+          <t>603178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>592184</t>
+          <t>595587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630786</t>
+          <t>630816</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175954</t>
+          <t>1175247</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1225237</t>
+          <t>1226748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51440</t>
+          <t>49885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>84748</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77415</t>
+          <t>77015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115918</t>
+          <t>114594</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>136593</t>
+          <t>137040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187225</t>
+          <t>186432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692101</t>
+          <t>694350</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727658</t>
+          <t>729213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>706660</t>
+          <t>707984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>745163</t>
+          <t>745563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1414451</t>
+          <t>1415244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1465083</t>
+          <t>1464636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>349516</t>
+          <t>351376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>429276</t>
+          <t>433553</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>448403</t>
+          <t>446382</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>533428</t>
+          <t>532027</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>822841</t>
+          <t>821373</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>934543</t>
+          <t>935342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2996094</t>
+          <t>2991817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3075854</t>
+          <t>3073994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3021670</t>
+          <t>3023071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3106695</t>
+          <t>3108716</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6045926</t>
+          <t>6045127</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6157628</t>
+          <t>6159096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50100</t>
+          <t>52262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27635</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60619</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95300</t>
+          <t>95453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243661</t>
+          <t>241499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267497</t>
+          <t>266586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236804</t>
+          <t>234326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261068</t>
+          <t>260316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>487164</t>
+          <t>487011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>521845</t>
+          <t>520982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43763</t>
+          <t>44097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73361</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59317</t>
+          <t>57780</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93536</t>
+          <t>90689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110449</t>
+          <t>110901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155286</t>
+          <t>153450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429214</t>
+          <t>431063</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458812</t>
+          <t>458478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429548</t>
+          <t>432395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463767</t>
+          <t>465304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>870373</t>
+          <t>872209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>915210</t>
+          <t>914758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72566</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>264632</t>
+          <t>265444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287617</t>
+          <t>287626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271831</t>
+          <t>271729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298143</t>
+          <t>299423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547003</t>
+          <t>546435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>582308</t>
+          <t>581304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35088</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>60079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43760</t>
+          <t>44214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72655</t>
+          <t>72123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83619</t>
+          <t>85507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123022</t>
+          <t>122859</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309086</t>
+          <t>309885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334876</t>
+          <t>334839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314628</t>
+          <t>315160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>343523</t>
+          <t>343069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634225</t>
+          <t>634388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>673628</t>
+          <t>671740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,71%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37623</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>42979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>46482</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76677</t>
+          <t>74323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173598</t>
+          <t>173260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192899</t>
+          <t>192182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175047</t>
+          <t>175608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195222</t>
+          <t>196156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353131</t>
+          <t>355485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383012</t>
+          <t>383326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>39462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40827</t>
+          <t>41236</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>43285</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72355</t>
+          <t>72317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224945</t>
+          <t>223661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244244</t>
+          <t>243795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232288</t>
+          <t>231879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253020</t>
+          <t>252874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463883</t>
+          <t>463921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494059</t>
+          <t>492953</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>56173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90819</t>
+          <t>90380</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56688</t>
+          <t>57033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91311</t>
+          <t>93184</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121723</t>
+          <t>123521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169682</t>
+          <t>173750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>565739</t>
+          <t>566178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599932</t>
+          <t>600385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>599983</t>
+          <t>598110</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>634606</t>
+          <t>634261</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1178170</t>
+          <t>1174102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1226129</t>
+          <t>1224331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63157</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96934</t>
+          <t>98434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95341</t>
+          <t>95164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137642</t>
+          <t>138209</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166451</t>
+          <t>167433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223402</t>
+          <t>221752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>681649</t>
+          <t>680149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>715426</t>
+          <t>714561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>688525</t>
+          <t>687958</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>730826</t>
+          <t>731003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1381348</t>
+          <t>1382998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1438299</t>
+          <t>1437317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>353501</t>
+          <t>353223</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>427026</t>
+          <t>424568</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>428803</t>
+          <t>427646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>514035</t>
+          <t>514429</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>802335</t>
+          <t>796559</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>915480</t>
+          <t>914997</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2967324</t>
+          <t>2969782</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3040849</t>
+          <t>3041127</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3030507</t>
+          <t>3030113</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3115739</t>
+          <t>3116896</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6023412</t>
+          <t>6023895</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6136557</t>
+          <t>6142333</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>52572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>45881</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>36322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83866</t>
+          <t>86031</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>72106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97978</t>
+          <t>102012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>271576</t>
+          <t>278695</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260069</t>
+          <t>266273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281616</t>
+          <t>288248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>245636</t>
+          <t>270180</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234854</t>
+          <t>260508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254017</t>
+          <t>279739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>517211</t>
+          <t>548875</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503099</t>
+          <t>532894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>531394</t>
+          <t>562800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44167</t>
+          <t>48666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73140</t>
+          <t>82672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67774</t>
+          <t>71077</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57055</t>
+          <t>59674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82226</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>126215</t>
+          <t>133669</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107473</t>
+          <t>113264</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145857</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>458088</t>
+          <t>466126</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443389</t>
+          <t>446046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>472362</t>
+          <t>480052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>445395</t>
+          <t>473558</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>430943</t>
+          <t>460330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456114</t>
+          <t>484961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>903483</t>
+          <t>939684</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>883841</t>
+          <t>919969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>922225</t>
+          <t>960089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>544635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>544635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513169</t>
+          <t>544635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029698</t>
+          <t>1073353</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029698</t>
+          <t>1073353</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029698</t>
+          <t>1073353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36141</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>58715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69602</t>
+          <t>70434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,22 +11453,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>105111</t>
+          <t>105798</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89805</t>
+          <t>90737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121128</t>
+          <t>120764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>268706</t>
+          <t>269186</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>257002</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279360</t>
+          <t>278446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>290811</t>
+          <t>296831</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>279526</t>
+          <t>285947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>301165</t>
+          <t>308274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,27 +11566,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>559518</t>
+          <t>566017</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>551051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>574824</t>
+          <t>581078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315501</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664629</t>
+          <t>671815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50337</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>44085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65118</t>
+          <t>75380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62981</t>
+          <t>67594</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39589</t>
+          <t>56347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>79979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113318</t>
+          <t>125672</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81067</t>
+          <t>108959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137329</t>
+          <t>146058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262220</t>
+          <t>315067</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247439</t>
+          <t>297765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274433</t>
+          <t>329060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>412737</t>
+          <t>354367</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391656</t>
+          <t>341982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>436129</t>
+          <t>365614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>674956</t>
+          <t>669435</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>650945</t>
+          <t>649049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>707207</t>
+          <t>686148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37178</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29948</t>
+          <t>31686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46172</t>
+          <t>49298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53389</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45669</t>
+          <t>48333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>64712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>95969</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78811</t>
+          <t>84198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104021</t>
+          <t>108125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>141564</t>
+          <t>165843</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132570</t>
+          <t>156367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148794</t>
+          <t>173979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>154047</t>
+          <t>169809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145578</t>
+          <t>161244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161767</t>
+          <t>177623</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>295611</t>
+          <t>335651</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>282157</t>
+          <t>323495</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307367</t>
+          <t>347422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207436</t>
+          <t>225956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386178</t>
+          <t>431620</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386178</t>
+          <t>431620</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386178</t>
+          <t>431620</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>56024</t>
+          <t>55001</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46517</t>
+          <t>45049</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67530</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37512</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>55490</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>101331</t>
+          <t>101431</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>88122</t>
+          <t>89193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115456</t>
+          <t>116472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>213612</t>
+          <t>215706</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202106</t>
+          <t>203582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223119</t>
+          <t>225658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>211080</t>
+          <t>216670</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201990</t>
+          <t>207609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218875</t>
+          <t>224277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>424692</t>
+          <t>432375</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>410567</t>
+          <t>417334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437901</t>
+          <t>444613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>98693</t>
+          <t>118694</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80694</t>
+          <t>98223</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117185</t>
+          <t>140359</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>323246</t>
+          <t>141583</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150158</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>629880</t>
+          <t>162314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>421939</t>
+          <t>260277</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245749</t>
+          <t>234107</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>858019</t>
+          <t>288019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>519959</t>
+          <t>594777</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>501467</t>
+          <t>573112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>537958</t>
+          <t>615248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>523290</t>
+          <t>626411</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216656</t>
+          <t>605680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>696378</t>
+          <t>643616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1043249</t>
+          <t>1221187</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>607169</t>
+          <t>1193445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1219439</t>
+          <t>1247357</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>618652</t>
+          <t>713471</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>618652</t>
+          <t>713471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>618652</t>
+          <t>713471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846536</t>
+          <t>767994</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846536</t>
+          <t>767994</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846536</t>
+          <t>767994</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1465188</t>
+          <t>1481464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1465188</t>
+          <t>1481464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1465188</t>
+          <t>1481464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>77316</t>
+          <t>86020</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33954</t>
+          <t>72538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>103275</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>101305</t>
+          <t>111223</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86571</t>
+          <t>93757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119732</t>
+          <t>126422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>178621</t>
+          <t>197243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>177167</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>218080</t>
+          <t>221178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>851404</t>
+          <t>712052</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818455</t>
+          <t>694797</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>894766</t>
+          <t>725534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>613542</t>
+          <t>718773</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>595115</t>
+          <t>703574</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>628276</t>
+          <t>736239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1464946</t>
+          <t>1430825</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1425487</t>
+          <t>1406890</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1537315</t>
+          <t>1450901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714847</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714847</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714847</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643567</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643567</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643567</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>464651</t>
+          <t>506606</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>365988</t>
+          <t>468873</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>515380</t>
+          <t>550434</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>756318</t>
+          <t>599485</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>572572</t>
+          <t>564001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1282956</t>
+          <t>633319</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1220969</t>
+          <t>1106090</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1019748</t>
+          <t>1055483</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1924356</t>
+          <t>1159513</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2987129</t>
+          <t>3017451</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2936400</t>
+          <t>2973623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3085792</t>
+          <t>3055184</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2896537</t>
+          <t>3126598</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2369899</t>
+          <t>3092764</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3080283</t>
+          <t>3162082</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5883666</t>
+          <t>6144050</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5180279</t>
+          <t>6090627</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6084887</t>
+          <t>6194657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3451780</t>
+          <t>3524057</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3652855</t>
+          <t>3726083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7104635</t>
+          <t>7250140</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
